--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAC6455-AE0C-42CE-9F2C-EAB4AB563DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609E1635-5C5E-4CA0-B076-1E54CFAF6992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6578" yWindow="2325" windowWidth="17984" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -530,7 +530,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -539,7 +539,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -766,8 +766,9 @@
   <cols>
     <col min="1" max="2" width="19.46484375" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.53125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.73046875" style="3" customWidth="1"/>
-    <col min="5" max="6" width="50.73046875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="36" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="13" customWidth="1"/>
     <col min="7" max="7" width="20.265625" style="3" customWidth="1"/>
     <col min="8" max="8" width="30.53125" style="3" customWidth="1"/>
     <col min="9" max="9" width="26.53125" style="3" customWidth="1"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609E1635-5C5E-4CA0-B076-1E54CFAF6992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C823A3B4-A2D1-411C-BBBC-6C947474553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6578" yWindow="2325" windowWidth="17984" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>Harvest</t>
   </si>
   <si>
     <t>10,1000</t>
-  </si>
-  <si>
-    <t>10,100</t>
   </si>
   <si>
     <t>int[]</t>
@@ -777,164 +774,164 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="14"/>
       <c r="F1" s="14"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.15">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>12</v>
-      </c>
       <c r="H3" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>37</v>
-      </c>
       <c r="H7" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
